--- a/astro-site/public/dl/kit-tareas-sushi-bar/06-tareas-perfiles.xlsx
+++ b/astro-site/public/dl/kit-tareas-sushi-bar/06-tareas-perfiles.xlsx
@@ -13,7 +13,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cocina Caliente" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sala y Servicio" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Itamae (Chef Sushi)'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Ayudante Sushi'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Cocina Caliente'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Sala y Servicio'!$4:$4</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -21,7 +26,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -66,6 +71,16 @@
       <color rgb="00999999"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="00666666"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -102,7 +117,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -122,10 +137,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C8E6C9"/>
+          <bgColor rgb="00C8E6C9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -486,14 +515,15 @@
   <sheetPr>
     <tabColor rgb="00C4974A"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B18"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -501,6 +531,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -508,6 +539,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="3" t="inlineStr">
         <is>
@@ -536,6 +568,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="B11" s="2" t="inlineStr">
         <is>
@@ -543,6 +576,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="B13" s="3" t="inlineStr">
         <is>
@@ -571,6 +605,7 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
     <row r="18">
       <c r="B18" s="2" t="inlineStr">
         <is>
@@ -578,8 +613,33 @@
         </is>
       </c>
     </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Marca con ✓ en la columna «✓ Completada» (desplegable): es la que cuenta el total de tareas completadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
+    <row r="22">
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-sushi-bar · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -588,7 +648,7 @@
   <sheetPr>
     <tabColor rgb="00C4974A"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -616,10 +676,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
@@ -644,7 +705,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -661,10 +722,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
@@ -690,10 +749,8 @@
       <c r="G6" s="10" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="13" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
@@ -719,10 +776,8 @@
       <c r="G7" s="10" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="13" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
@@ -748,10 +803,8 @@
       <c r="G8" s="10" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="13" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
@@ -777,10 +830,8 @@
       <c r="G9" s="10" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="13" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
@@ -806,10 +857,8 @@
       <c r="G10" s="10" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A11" s="13" t="n">
+        <v>6</v>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
@@ -835,10 +884,8 @@
       <c r="G11" s="10" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A12" s="13" t="n">
+        <v>7</v>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
@@ -864,10 +911,8 @@
       <c r="G12" s="10" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="13" t="n">
+        <v>8</v>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
@@ -893,10 +938,8 @@
       <c r="G13" s="10" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="13" t="n">
+        <v>9</v>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
@@ -922,10 +965,8 @@
       <c r="G14" s="10" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="13" t="n">
+        <v>10</v>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
@@ -950,6 +991,27 @@
       <c r="F15" s="9" t="n"/>
       <c r="G15" s="10" t="n"/>
     </row>
+    <row r="16"/>
+    <row r="17">
+      <c r="A17" s="14" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="D17">
+        <f>COUNTIF(F5:F15,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F17">
+        <f>COUNTIF(B5:B15,"?*")</f>
+        <v>10.0</v>
+      </c>
+    </row>
     <row r="18">
       <c r="B18" s="12" t="inlineStr">
         <is>
@@ -966,11 +1028,30 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A2:G2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <conditionalFormatting sqref="A5:G15">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F12 F13 F14 F15" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -979,7 +1060,7 @@
   <sheetPr>
     <tabColor rgb="004A90C4"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1007,10 +1088,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
@@ -1035,7 +1117,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -1052,10 +1134,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
@@ -1081,10 +1161,8 @@
       <c r="G6" s="10" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="13" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
@@ -1110,10 +1188,8 @@
       <c r="G7" s="10" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="13" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
@@ -1139,10 +1215,8 @@
       <c r="G8" s="10" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="13" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
@@ -1168,10 +1242,8 @@
       <c r="G9" s="10" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="13" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
@@ -1197,10 +1269,8 @@
       <c r="G10" s="10" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A11" s="13" t="n">
+        <v>6</v>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
@@ -1226,10 +1296,8 @@
       <c r="G11" s="10" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A12" s="13" t="n">
+        <v>7</v>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
@@ -1255,10 +1323,8 @@
       <c r="G12" s="10" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="13" t="n">
+        <v>8</v>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
@@ -1283,6 +1349,27 @@
       <c r="F13" s="9" t="n"/>
       <c r="G13" s="10" t="n"/>
     </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="D15">
+        <f>COUNTIF(F5:F13,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F15">
+        <f>COUNTIF(B5:B13,"?*")</f>
+        <v>8.0</v>
+      </c>
+    </row>
     <row r="16">
       <c r="B16" s="12" t="inlineStr">
         <is>
@@ -1299,11 +1386,30 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A2:G2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <conditionalFormatting sqref="A5:G13">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F12 F13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1312,7 +1418,7 @@
   <sheetPr>
     <tabColor rgb="00E65100"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1340,10 +1446,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
@@ -1368,7 +1475,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -1385,10 +1492,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
@@ -1414,10 +1519,8 @@
       <c r="G6" s="10" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="13" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
@@ -1443,10 +1546,8 @@
       <c r="G7" s="10" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="13" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
@@ -1472,10 +1573,8 @@
       <c r="G8" s="10" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="13" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
@@ -1501,10 +1600,8 @@
       <c r="G9" s="10" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="13" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
@@ -1530,10 +1627,8 @@
       <c r="G10" s="10" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A11" s="13" t="n">
+        <v>6</v>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
@@ -1558,6 +1653,27 @@
       <c r="F11" s="9" t="n"/>
       <c r="G11" s="10" t="n"/>
     </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="D13">
+        <f>COUNTIF(F5:F11,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F13">
+        <f>COUNTIF(B5:B11,"?*")</f>
+        <v>6.0</v>
+      </c>
+    </row>
     <row r="14">
       <c r="B14" s="12" t="inlineStr">
         <is>
@@ -1574,11 +1690,30 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A2:G2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <conditionalFormatting sqref="A5:G11">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1587,7 +1722,7 @@
   <sheetPr>
     <tabColor rgb="00388E3C"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1615,10 +1750,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="7" t="inlineStr">
@@ -1643,7 +1779,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -1660,10 +1796,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="13" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
@@ -1689,10 +1823,8 @@
       <c r="G6" s="10" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="13" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
@@ -1718,10 +1850,8 @@
       <c r="G7" s="10" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="13" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
@@ -1747,10 +1877,8 @@
       <c r="G8" s="10" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="13" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
@@ -1776,10 +1904,8 @@
       <c r="G9" s="10" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="13" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
@@ -1805,10 +1931,8 @@
       <c r="G10" s="10" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A11" s="13" t="n">
+        <v>6</v>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
@@ -1834,10 +1958,8 @@
       <c r="G11" s="10" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A12" s="13" t="n">
+        <v>7</v>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
@@ -1863,10 +1985,8 @@
       <c r="G12" s="10" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="13" t="n">
+        <v>8</v>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
@@ -1892,10 +2012,8 @@
       <c r="G13" s="10" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="13" t="n">
+        <v>9</v>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
@@ -1920,6 +2038,27 @@
       <c r="F14" s="9" t="n"/>
       <c r="G14" s="10" t="n"/>
     </row>
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="D16">
+        <f>COUNTIF(F5:F14,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="F16">
+        <f>COUNTIF(B5:B14,"?*")</f>
+        <v>9.0</v>
+      </c>
+    </row>
     <row r="17">
       <c r="B17" s="12" t="inlineStr">
         <is>
@@ -1936,10 +2075,29 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A2:G2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <conditionalFormatting sqref="A5:G14">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F12 F13 F14" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>